--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486825_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486825_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>12.2461</v>
+        <v>10.8117</v>
       </c>
       <c r="E2" t="n">
-        <v>7.4747</v>
+        <v>6.9094</v>
       </c>
       <c r="F2" t="n">
-        <v>4.7714</v>
+        <v>3.9023</v>
       </c>
       <c r="G2" t="n">
         <v>8.861000000000001</v>
@@ -610,13 +610,13 @@
         <v>2.3169</v>
       </c>
       <c r="S2" t="n">
-        <v>2.4277</v>
+        <v>0.9932</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3305</v>
+        <v>-0.2349</v>
       </c>
       <c r="U2" t="n">
-        <v>2.0972</v>
+        <v>1.2281</v>
       </c>
       <c r="V2" t="n">
         <v>0.5712</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>10.5088</v>
+        <v>10.6453</v>
       </c>
       <c r="E3" t="n">
-        <v>6.3029</v>
+        <v>6.6132</v>
       </c>
       <c r="F3" t="n">
-        <v>4.2059</v>
+        <v>4.0321</v>
       </c>
       <c r="G3" t="n">
         <v>8.571</v>
@@ -688,13 +688,13 @@
         <v>1.5446</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0224</v>
+        <v>0.1588</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.607</v>
+        <v>-0.2967</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6294</v>
+        <v>0.4555</v>
       </c>
       <c r="V3" t="n">
         <v>0.3709</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.881</v>
+        <v>5.1749</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7138</v>
+        <v>1.6104</v>
       </c>
       <c r="F4" t="n">
-        <v>3.1672</v>
+        <v>3.5645</v>
       </c>
       <c r="G4" t="n">
         <v>6.3539</v>
@@ -766,13 +766,13 @@
         <v>1.7377</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3145</v>
+        <v>-0.0206</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.08309999999999999</v>
+        <v>-0.1865</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2314</v>
+        <v>0.1659</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I. CONDES LOPEZ-CEPERO</t>
+          <t>J. BALDERAS MARTÍN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3881</v>
+        <v>2.1718</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.6086</v>
+        <v>0.5551</v>
       </c>
       <c r="F5" t="n">
-        <v>1.9967</v>
+        <v>1.6167</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.3054</v>
+        <v>0.6106</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5243</v>
+        <v>0.7304</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.8297</v>
+        <v>-0.1198</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.2496</v>
+        <v>0.8048999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3178</v>
+        <v>1.4898</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5674</v>
+        <v>-0.6849</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0558</v>
+        <v>-0.1943</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2065</v>
+        <v>-0.7594</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2623</v>
+        <v>0.5651</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.5792</v>
+        <v>2.1239</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9308</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3515</v>
+        <v>2.1239</v>
       </c>
       <c r="S5" t="n">
-        <v>2.2727</v>
+        <v>-0.2344</v>
       </c>
       <c r="T5" t="n">
-        <v>1.5718</v>
+        <v>-0.2072</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7009</v>
+        <v>-0.0272</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.3282</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>-0.0426</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2028</v>
+        <v>1.2276</v>
       </c>
       <c r="E6" t="n">
         <v>1.072</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1308</v>
+        <v>0.1556</v>
       </c>
       <c r="G6" t="n">
         <v>1.6649</v>
@@ -922,13 +922,13 @@
         <v>0.1931</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3696</v>
+        <v>-0.3448</v>
       </c>
       <c r="T6" t="n">
         <v>-0.1104</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2592</v>
+        <v>-0.2344</v>
       </c>
       <c r="V6" t="n">
         <v>-0.2856</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. BALDERAS MARTÍN</t>
+          <t>I. CONDES LOPEZ-CEPERO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0491</v>
+        <v>-0.0227</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1206</v>
+        <v>-1.7462</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1697</v>
+        <v>1.7235</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6106</v>
+        <v>-0.3054</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7304</v>
+        <v>0.5243</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1198</v>
+        <v>-0.8297</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8048999999999999</v>
+        <v>-0.2496</v>
       </c>
       <c r="K7" t="n">
-        <v>1.4898</v>
+        <v>0.3178</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6849</v>
+        <v>-0.5674</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1943</v>
+        <v>-0.0558</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7594</v>
+        <v>0.2065</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5651</v>
+        <v>-0.2623</v>
       </c>
       <c r="P7" t="n">
-        <v>2.1239</v>
+        <v>-0.5792</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.9308</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1239</v>
+        <v>1.3515</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.3571</v>
+        <v>0.8619</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8829</v>
+        <v>0.4342</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4742</v>
+        <v>0.4278</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3282</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.0426</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6289</v>
+        <v>-0.2979</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.5811</v>
+        <v>-1.3742</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9522</v>
+        <v>1.0763</v>
       </c>
       <c r="G8" t="n">
         <v>0.2181</v>
@@ -1078,13 +1078,13 @@
         <v>1.1585</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4688</v>
+        <v>-0.1378</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5518</v>
+        <v>-0.345</v>
       </c>
       <c r="U8" t="n">
-        <v>0.083</v>
+        <v>0.2072</v>
       </c>
       <c r="V8" t="n">
         <v>-0.5712</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0946</v>
+        <v>-0.3485</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.9406</v>
+        <v>-2.3683</v>
       </c>
       <c r="F9" t="n">
-        <v>1.846</v>
+        <v>2.0198</v>
       </c>
       <c r="G9" t="n">
         <v>1.1617</v>
@@ -1156,13 +1156,13 @@
         <v>1.9308</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.2908</v>
+        <v>-0.5447</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7174</v>
+        <v>-0.1451</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5735</v>
+        <v>-0.3997</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.9772</v>
+        <v>-1.9523</v>
       </c>
       <c r="E10" t="n">
         <v>-1.7797</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1974</v>
+        <v>-0.1726</v>
       </c>
       <c r="G10" t="n">
         <v>-0.5043</v>
@@ -1234,13 +1234,13 @@
         <v>0.1931</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7006</v>
+        <v>-0.6757</v>
       </c>
       <c r="T10" t="n">
         <v>-0.1655</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.535</v>
+        <v>-0.5102</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.4171</v>
+        <v>-2.4902</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.6481</v>
+        <v>-2.6963</v>
       </c>
       <c r="F11" t="n">
-        <v>0.231</v>
+        <v>0.2061</v>
       </c>
       <c r="G11" t="n">
         <v>-1.8488</v>
@@ -1312,13 +1312,13 @@
         <v>1.5446</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1821</v>
+        <v>-0.2552</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0279</v>
+        <v>-0.0761</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1542</v>
+        <v>-0.179</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.1348</v>
+        <v>-2.6204</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.5892</v>
+        <v>-2.2238</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5456</v>
+        <v>-0.3966</v>
       </c>
       <c r="G12" t="n">
         <v>-0.3005</v>
@@ -1390,13 +1390,13 @@
         <v>1.3515</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.0041</v>
+        <v>-0.4896</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5518</v>
+        <v>-0.1864</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4523</v>
+        <v>-0.3033</v>
       </c>
       <c r="V12" t="n">
         <v>-0.2856</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>22.0233</v>
+        <v>22.2993</v>
       </c>
       <c r="E13" t="n">
-        <v>4.295500000000001</v>
+        <v>4.5716</v>
       </c>
       <c r="F13" t="n">
-        <v>17.7279</v>
+        <v>17.7277</v>
       </c>
       <c r="G13" t="n">
         <v>24.4822</v>
@@ -1459,7 +1459,7 @@
         <v>5.617100000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.9653000000000004</v>
+        <v>-0.9653000000000002</v>
       </c>
       <c r="Q13" t="n">
         <v>-16.4118</v>
@@ -1468,13 +1468,13 @@
         <v>15.4462</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9647999999999994</v>
+        <v>-0.6889000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.7955</v>
+        <v>-1.5196</v>
       </c>
       <c r="U13" t="n">
-        <v>0.8307</v>
+        <v>0.8306999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>-0.5285</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.2291</v>
+        <v>1.4307</v>
       </c>
       <c r="E14" t="n">
-        <v>3.1654</v>
+        <v>2.4414</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.9362</v>
+        <v>-1.0107</v>
       </c>
       <c r="G14" t="n">
         <v>-1.642</v>
@@ -1546,13 +1546,13 @@
         <v>2.1239</v>
       </c>
       <c r="S14" t="n">
-        <v>0.9983</v>
+        <v>0.1999</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5788</v>
+        <v>-0.1452</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4196</v>
+        <v>0.3451</v>
       </c>
       <c r="V14" t="n">
         <v>0.9421</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>I. CORREA BOULATOVA</t>
+          <t>K. LOPEZ MARQUEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.031</v>
+        <v>0.9066</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6952</v>
+        <v>1.6893</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3358</v>
+        <v>-0.7827</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.1538</v>
+        <v>0.9578</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8274</v>
+        <v>2.1311</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.9812</v>
+        <v>-1.1733</v>
       </c>
       <c r="J15" t="n">
-        <v>1.5298</v>
+        <v>2.9997</v>
       </c>
       <c r="K15" t="n">
-        <v>1.4485</v>
+        <v>2.959</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0814</v>
+        <v>0.0407</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.6837</v>
+        <v>-2.0418</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6211</v>
+        <v>-0.8278</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.0626</v>
+        <v>-1.214</v>
       </c>
       <c r="P15" t="n">
-        <v>1.7377</v>
+        <v>0.1931</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.1585</v>
       </c>
       <c r="R15" t="n">
-        <v>1.7377</v>
+        <v>1.3515</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4744</v>
+        <v>0.0413</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1927</v>
+        <v>-0.1519</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2817</v>
+        <v>0.1932</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.0273</v>
+        <v>-0.2856</v>
       </c>
       <c r="W15" t="n">
-        <v>-1.0273</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>K. LOPEZ MARQUEZ</t>
+          <t>I. CORREA BOULATOVA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6998</v>
+        <v>0.7289</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4825</v>
+        <v>0.5918</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.7827</v>
+        <v>0.1371</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9578</v>
+        <v>-0.1538</v>
       </c>
       <c r="H16" t="n">
-        <v>2.1311</v>
+        <v>0.8274</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.1733</v>
+        <v>-0.9812</v>
       </c>
       <c r="J16" t="n">
-        <v>2.9997</v>
+        <v>1.5298</v>
       </c>
       <c r="K16" t="n">
-        <v>2.959</v>
+        <v>1.4485</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0407</v>
+        <v>0.0814</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.0418</v>
+        <v>-1.6837</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.8278</v>
+        <v>-0.6211</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.214</v>
+        <v>-1.0626</v>
       </c>
       <c r="P16" t="n">
-        <v>0.1931</v>
+        <v>1.7377</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1585</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3515</v>
+        <v>1.7377</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1655</v>
+        <v>0.1724</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3587</v>
+        <v>0.0893</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1932</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.2856</v>
+        <v>-1.0273</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>-1.0273</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1735,10 +1735,10 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2323</v>
+        <v>-0.6459</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0213</v>
+        <v>-0.435</v>
       </c>
       <c r="F17" t="n">
         <v>-0.2109</v>
@@ -1780,10 +1780,10 @@
         <v>1.7377</v>
       </c>
       <c r="S17" t="n">
-        <v>1.2686</v>
+        <v>0.8549</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5786</v>
+        <v>0.165</v>
       </c>
       <c r="U17" t="n">
         <v>0.6899999999999999</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.7581</v>
+        <v>-1.1251</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.7448</v>
+        <v>-1.4346</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0133</v>
+        <v>0.3095</v>
       </c>
       <c r="G18" t="n">
         <v>-0.925</v>
@@ -1858,13 +1858,13 @@
         <v>1.7377</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.447</v>
+        <v>0.1861</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5795</v>
+        <v>-0.2692</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1325</v>
+        <v>0.4553</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.2359</v>
+        <v>-2.091</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4559</v>
+        <v>-1.5593</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7801</v>
+        <v>-0.5318000000000001</v>
       </c>
       <c r="G19" t="n">
         <v>-1.3532</v>
@@ -1936,13 +1936,13 @@
         <v>1.1585</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1105</v>
+        <v>0.0344</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4135</v>
+        <v>0.31</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5239</v>
+        <v>-0.2756</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.622</v>
+        <v>-3.593</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.8961</v>
+        <v>-2.7927</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7258</v>
+        <v>-0.8003</v>
       </c>
       <c r="G20" t="n">
         <v>-2.1657</v>
@@ -2014,13 +2014,13 @@
         <v>0.9654</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2978</v>
+        <v>-0.2689</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1655</v>
+        <v>-0.0621</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1323</v>
+        <v>-0.2068</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.3732</v>
+        <v>-4.9139</v>
       </c>
       <c r="E21" t="n">
-        <v>-6.2028</v>
+        <v>-5.8925</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8296</v>
+        <v>0.9786</v>
       </c>
       <c r="G21" t="n">
         <v>-3.4314</v>
@@ -2092,13 +2092,13 @@
         <v>1.5446</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5903</v>
+        <v>-0.131</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.276</v>
+        <v>0.0342</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3142</v>
+        <v>-0.1652</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.5495</v>
+        <v>-5.3883</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.4463</v>
+        <v>-3.136</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.1032</v>
+        <v>-2.2522</v>
       </c>
       <c r="G22" t="n">
         <v>-7.0116</v>
@@ -2170,13 +2170,13 @@
         <v>1.9308</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4028</v>
+        <v>-0.2415</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9933999999999999</v>
+        <v>-0.6831</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5906</v>
+        <v>0.4416</v>
       </c>
       <c r="V22" t="n">
         <v>0.8995</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.2123</v>
+        <v>-7.3324</v>
       </c>
       <c r="E23" t="n">
-        <v>-7.3037</v>
+        <v>-7.2002</v>
       </c>
       <c r="F23" t="n">
-        <v>0.09130000000000001</v>
+        <v>-0.1321</v>
       </c>
       <c r="G23" t="n">
         <v>-5.8044</v>
@@ -2248,13 +2248,13 @@
         <v>2.1239</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2373</v>
+        <v>0.1172</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2211</v>
+        <v>-0.1177</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4584</v>
+        <v>0.2349</v>
       </c>
       <c r="V23" t="n">
         <v>0.2856</v>
@@ -2287,7 +2287,7 @@
         <v>-17.7278</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.2955</v>
+        <v>-4.295500000000001</v>
       </c>
       <c r="G24" t="n">
         <v>-24.4822</v>
@@ -2326,10 +2326,10 @@
         <v>16.4117</v>
       </c>
       <c r="S24" t="n">
-        <v>0.9646999999999999</v>
+        <v>0.9647999999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8306</v>
+        <v>-0.8307000000000001</v>
       </c>
       <c r="U24" t="n">
         <v>1.7956</v>
